--- a/tame_output/ON/bt/strategyON_20231115.xlsx
+++ b/tame_output/ON/bt/strategyON_20231115.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,16 +758,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.4%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.2%</t>
+          <t>452.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.7%</t>
+          <t>103.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,16 +1064,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.8%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.9%</t>
+          <t>133.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.8%</t>
+          <t>127.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>28.3%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1781"/>
+  <dimension ref="A1:G1782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.11753708665523</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42489,6 +42489,29 @@
       </c>
       <c r="G1781" t="n">
         <v>4.378246358032915</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="2" t="n">
+        <v>45244</v>
+      </c>
+      <c r="B1782" t="n">
+        <v>3.092915099060805</v>
+      </c>
+      <c r="C1782" t="n">
+        <v>3.078959898064911</v>
+      </c>
+      <c r="D1782" t="n">
+        <v>1.560559925537222</v>
+      </c>
+      <c r="E1782" t="n">
+        <v>3.702827443966052</v>
+      </c>
+      <c r="F1782" t="n">
+        <v>2.190192151603434</v>
+      </c>
+      <c r="G1782" t="n">
+        <v>4.393075189026972</v>
       </c>
     </row>
   </sheetData>
